--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.4529</v>
+        <v>17.88854</v>
       </c>
       <c r="D2" t="n">
-        <v>17.4671</v>
+        <v>17.44379</v>
       </c>
       <c r="E2" t="n">
-        <v>17.46536</v>
+        <v>17.58824</v>
       </c>
       <c r="F2" t="n">
-        <v>44.49493</v>
+        <v>43.97757</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05371</v>
+        <v>0.05372</v>
       </c>
       <c r="H2" t="n">
-        <v>1.87059</v>
+        <v>1.86078</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.58585</v>
+        <v>17.72075</v>
       </c>
       <c r="D3" t="n">
-        <v>17.26891</v>
+        <v>17.04873</v>
       </c>
       <c r="E3" t="n">
-        <v>17.63466</v>
+        <v>17.71726</v>
       </c>
       <c r="F3" t="n">
-        <v>44.7558</v>
+        <v>44.42151</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05308</v>
+        <v>0.05297</v>
       </c>
       <c r="H3" t="n">
-        <v>1.90242</v>
+        <v>1.90078</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.71937</v>
+        <v>17.48814</v>
       </c>
       <c r="D4" t="n">
-        <v>17.48346</v>
+        <v>17.22459</v>
       </c>
       <c r="E4" t="n">
-        <v>17.4726</v>
+        <v>17.33342</v>
       </c>
       <c r="F4" t="n">
-        <v>44.88974</v>
+        <v>44.0631</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05357</v>
+        <v>0.05356</v>
       </c>
       <c r="H4" t="n">
-        <v>1.90425</v>
+        <v>1.92928</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.89992</v>
+        <v>17.56401</v>
       </c>
       <c r="D6" t="n">
-        <v>16.58728</v>
+        <v>16.10185</v>
       </c>
       <c r="E6" t="n">
-        <v>17.20313</v>
+        <v>17.16074</v>
       </c>
       <c r="F6" t="n">
-        <v>22.79711</v>
+        <v>22.56454</v>
       </c>
       <c r="G6" t="n">
-        <v>35.59934</v>
+        <v>36.10962</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.55218</v>
+        <v>17.36174</v>
       </c>
       <c r="D7" t="n">
-        <v>16.69586</v>
+        <v>16.89702</v>
       </c>
       <c r="E7" t="n">
-        <v>17.00091</v>
+        <v>16.95757</v>
       </c>
       <c r="F7" t="n">
-        <v>22.80913</v>
+        <v>22.83064</v>
       </c>
       <c r="G7" t="n">
-        <v>35.67263</v>
+        <v>36.06092</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.74475</v>
+        <v>17.65495</v>
       </c>
       <c r="D8" t="n">
-        <v>16.51095</v>
+        <v>16.47826</v>
       </c>
       <c r="E8" t="n">
-        <v>16.79259</v>
+        <v>16.92976</v>
       </c>
       <c r="F8" t="n">
-        <v>22.55908</v>
+        <v>22.62452</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58152</v>
+        <v>36.26138</v>
       </c>
     </row>
   </sheetData>
